--- a/output/2026-09-13_02_Croazia_Varazdinska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-13_02_Croazia_Varazdinska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore B2B di utensili, macchine utensili, pneumatica e idraulica; attivo dal 1994; sede in Zinke Kunc 25, Varaždin. Verificato tramite ricerca web (segment.hr, tvrtke.hr, Kompass) - telefono e email confermati.</t>
+          <t>Distributore B2B di utensili, macchine utensili, pneumatica e idraulica; attivo dal 1994; sede in Zinke Kunc 25, Varaždin. Verificato tramite ricerca web (segment.hr, tvrtke.hr, Kompass) - telefono e email confermati. [DUPLICATO — vedi anche: 2026-09-13_00_Croazia_Varazdinska_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Distributore autorizzato multi-brand (Unior, Makita, Bosch, Rems, Rodcraft, Mark, ecc.) di utensili, macchine e attrezzature; sede a Novi Marof e filiale a Ludbreg. Verificato (comet.hr, companywall.hr, fininfo.hr) - telefono e email confermati.</t>
+          <t>Distributore autorizzato multi-brand (Unior, Makita, Bosch, Rems, Rodcraft, Mark, ecc.) di utensili, macchine e attrezzature; sede a Novi Marof e filiale a Ludbreg. Verificato (comet.hr, companywall.hr, fininfo.hr) - telefono e email confermati. [DUPLICATO — vedi anche: 2026-09-12_22_Croazia_Varazdinska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">

--- a/output/2026-09-13_02_Croazia_Varazdinska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-13_02_Croazia_Varazdinska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
